--- a/backend/data/financials_by_company/1869.HK.xlsx
+++ b/backend/data/financials_by_company/1869.HK.xlsx
@@ -4355,7 +4355,7 @@
         <v>-4685000</v>
       </c>
       <c r="BM2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BN2" t="n">
         <v>1.456</v>
@@ -4606,7 +4606,7 @@
         <v>0</v>
       </c>
       <c r="ED2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE2" t="n">
         <v>-6.000005</v>
